--- a/output/full_scan/batch_seq8_2026-08-06.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-06.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7792</v>
+        <v>7828</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>579.888905994521</v>
+        <v>600.9718037536712</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>217</v>
+        <v>1755</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>48.34223076591411</v>
+        <v>51.18269234820194</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>34.56275343233892</v>
+        <v>17.88182026820561</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.374050825089527</v>
+        <v>0.3003755495813536</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.364623909763332</v>
+        <v>0.4826455936930074</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6958</v>
+        <v>7792</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>576.7718964330768</v>
+        <v>579.888905994521</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>18.45</v>
+        <v>217</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>57.00024510305532</v>
+        <v>48.34223076591411</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.16432662021577</v>
+        <v>34.56275343233892</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.6992063553836295</v>
+        <v>2.374050825089527</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.0284028684209368</v>
+        <v>2.364623909763332</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>8039</v>
+        <v>6958</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>569.7903550492945</v>
+        <v>576.7718964330768</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>216</v>
+        <v>18.45</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>58.60748260902537</v>
+        <v>57.00024510305532</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>25.59128774416592</v>
+        <v>30.16432662021577</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.9713640885808495</v>
+        <v>0.6992063553836295</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-0.7520603211629222</v>
+        <v>0.0284028684209368</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6949</v>
+        <v>8039</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>565.3493884824181</v>
+        <v>569.7903550492945</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>977</v>
+        <v>216</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,13 +976,13 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>57.68686762926969</v>
+        <v>58.60748260902537</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>26.37021930715196</v>
+        <v>25.59128774416592</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6151338190557073</v>
+        <v>0.9713640885808495</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-7.120572440740071</v>
+        <v>-0.7520603211629222</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>8016</v>
+        <v>6949</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>555.4459673460004</v>
+        <v>565.3493884824181</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>308.5</v>
+        <v>977</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>55.63008455127415</v>
+        <v>57.68686762926969</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>17.99343984928558</v>
+        <v>26.37021930715196</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.9644024463741614</v>
+        <v>0.6151338190557073</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>1.247671001841403</v>
+        <v>-7.120572440740071</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7750</v>
+        <v>8016</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>543.3531352012402</v>
+        <v>555.4459673460004</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2365</v>
+        <v>308.5</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>60.27545487204324</v>
+        <v>55.63008455127415</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>17.18797733343309</v>
+        <v>17.99343984928558</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.882167149059334</v>
+        <v>0.9644024463741614</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>57.29016140320334</v>
+        <v>1.247671001841403</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6952</v>
+        <v>7750</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>536.2302622609308</v>
+        <v>543.3531352012402</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>37</v>
+        <v>2365</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>61.52543618521493</v>
+        <v>60.27545487204324</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>25.39807582418051</v>
+        <v>17.18797733343309</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.5591873960052075</v>
+        <v>1.882167149059334</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>0.193516330143653</v>
+        <v>57.29016140320334</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7751</v>
+        <v>6952</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>523.2017998807307</v>
+        <v>536.2302622609308</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1405</v>
+        <v>37</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.29673496093108</v>
+        <v>61.52543618521493</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>14.225949622081</v>
+        <v>25.39807582418051</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.9201799880730795</v>
+        <v>0.5591873960052075</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>39.96308277340527</v>
+        <v>0.193516330143653</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6996</v>
+        <v>7751</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>522.4248372095342</v>
+        <v>523.2017998807307</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>186</v>
+        <v>1405</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>55.56701577618455</v>
+        <v>56.29673496093108</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>21.26570348523213</v>
+        <v>14.225949622081</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.460772803942354</v>
+        <v>0.9201799880730795</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.531170611287356</v>
+        <v>39.96308277340527</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6955</v>
+        <v>6996</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>511.401523413601</v>
+        <v>522.4248372095342</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>122.5</v>
+        <v>186</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>52.50046364459856</v>
+        <v>55.56701577618455</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>8.970221786496309</v>
+        <v>21.26570348523213</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.1829351660271075</v>
+        <v>1.460772803942354</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>1.123435360298551</v>
+        <v>1.531170611287356</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6855</v>
+        <v>6955</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>489.2507706168951</v>
+        <v>511.401523413601</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>117</v>
+        <v>122.5</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>51.7293935854424</v>
+        <v>52.50046364459856</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>5.654432944744989</v>
+        <v>8.970221786496309</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.618045592220628</v>
+        <v>0.1829351660271075</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>2.415449776638063</v>
+        <v>1.123435360298551</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7711</v>
+        <v>6855</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>483.5834232890475</v>
+        <v>489.2507706168951</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>361.5</v>
+        <v>117</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.4603034684668</v>
+        <v>51.7293935854424</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>33.44164147906876</v>
+        <v>5.654432944744989</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.022726331978404</v>
+        <v>1.618045592220628</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>7.52978854434758</v>
+        <v>2.415449776638063</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6914</v>
+        <v>7711</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>475.1765684700295</v>
+        <v>483.5834232890475</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>146.5</v>
+        <v>361.5</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.96719086566379</v>
+        <v>67.4603034684668</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>16.53135550062127</v>
+        <v>33.44164147906876</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.4388793044977842</v>
+        <v>1.022726331978404</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.09333343374332601</v>
+        <v>7.52978854434758</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, bb_squeeze_breakout</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7715</v>
+        <v>6914</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>464.0634758964953</v>
+        <v>475.1765684700295</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>36</v>
+        <v>146.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>60.54808349684752</v>
+        <v>56.96719086566379</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>25.4417383390125</v>
+        <v>16.53135550062127</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.257096207211458</v>
+        <v>0.4388793044977842</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>0.3344459863227541</v>
+        <v>0.09333343374332601</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6922</v>
+        <v>7715</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>459.6102985597597</v>
+        <v>464.0634758964953</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>194.5</v>
+        <v>36</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.86309441426074</v>
+        <v>60.54808349684752</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>14.52418101218289</v>
+        <v>25.4417383390125</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.036424168896783</v>
+        <v>1.257096207211458</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>1.864550429438967</v>
+        <v>0.3344459863227541</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7714</v>
+        <v>6922</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>449.7647117559799</v>
+        <v>459.6102985597597</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>153.5</v>
+        <v>194.5</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>48.92956356137245</v>
+        <v>59.86309441426074</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>24.47724280011043</v>
+        <v>14.52418101218289</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.4109666876992023</v>
+        <v>1.036424168896783</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-3.132359375455525</v>
+        <v>1.864550429438967</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6957</v>
+        <v>7714</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>446.9245947459977</v>
+        <v>449.7647117559799</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>210</v>
+        <v>153.5</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>45.3464188552359</v>
+        <v>48.92956356137245</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>29.92283445044182</v>
+        <v>24.47724280011043</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.3538626660173334</v>
+        <v>0.4109666876992023</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-4.898542605097596</v>
+        <v>-3.132359375455525</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6907</v>
+        <v>6957</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>445.8367964360891</v>
+        <v>446.9245947459977</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>54.62846195399493</v>
+        <v>45.3464188552359</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>24.90369619135765</v>
+        <v>29.92283445044182</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.420938502716849</v>
+        <v>0.3538626660173334</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>-3.762683595311465</v>
+        <v>-4.898542605097596</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8043</v>
+        <v>6907</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>蜜望實</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>435.948231956348</v>
+        <v>445.8367964360891</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>135</v>
+        <v>195</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>42.88027482803757</v>
+        <v>54.62846195399493</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>24.34034374816646</v>
+        <v>24.90369619135765</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.5141213247051183</v>
+        <v>1.420938502716849</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>1</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.2470483441460871</v>
+        <v>-3.762683595311465</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7712</v>
+        <v>8043</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>蜜望實</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>434.8771024180089</v>
+        <v>435.948231956348</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45.21779250240709</v>
+        <v>42.88027482803757</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>26.84948302510635</v>
+        <v>24.34034374816646</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.7875679116596298</v>
+        <v>0.5141213247051183</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>0.5380434237218239</v>
+        <v>0.2470483441460871</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1852,21 +1852,21 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6910</v>
+        <v>7712</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>425.0691507746158</v>
+        <v>434.8771024180089</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>24.7</v>
+        <v>142</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>41.10665745155072</v>
+        <v>45.21779250240709</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>25.59110240555217</v>
+        <v>26.84948302510635</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>1.719319270726669</v>
+        <v>0.7875679116596298</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0648429725483734</v>
+        <v>0.5380434237218239</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7689</v>
+        <v>6910</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>415.4019761415498</v>
+        <v>425.0691507746158</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>164</v>
+        <v>24.7</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>18.73748763550472</v>
+        <v>41.10665745155072</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>30.70526298413127</v>
+        <v>25.59110240555217</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.740197614154974</v>
+        <v>1.719319270726669</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-2.875998878588732</v>
+        <v>0.0648429725483734</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>8044</v>
+        <v>7689</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>網家</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>406.2590482792534</v>
+        <v>415.4019761415498</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>27.35</v>
+        <v>164</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>53.03021171723922</v>
+        <v>18.73748763550472</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.85551947478458</v>
+        <v>30.70526298413127</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7286997569903049</v>
+        <v>1.740197614154974</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.1417750948892058</v>
+        <v>-2.875998878588732</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6947</v>
+        <v>8044</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>網家</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>392.1248394803898</v>
+        <v>406.2590482792534</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>81.59999999999999</v>
+        <v>27.35</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>53.55217245562648</v>
+        <v>53.03021171723922</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>20.26865909880749</v>
+        <v>16.85551947478458</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8294257710350541</v>
+        <v>0.7286997569903049</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.7008035399600154</v>
+        <v>0.1417750948892058</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, foreign_buy_3d, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7717</v>
+        <v>6947</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>386.926368396432</v>
+        <v>392.1248394803898</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>427</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>47.59639318424159</v>
+        <v>53.55217245562648</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>26.28620467657263</v>
+        <v>20.26865909880749</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.6525482008037098</v>
+        <v>0.8294257710350541</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>6.40100104353121</v>
+        <v>0.7008035399600154</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7839</v>
+        <v>7717</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>384.0178886326881</v>
+        <v>386.926368396432</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>45.75</v>
+        <v>427</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>48.82833316893743</v>
+        <v>47.59639318424159</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.3020451412452</v>
+        <v>26.28620467657263</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.686103248940633</v>
+        <v>0.6525482008037098</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.3973073263924779</v>
+        <v>6.40100104353121</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7822</v>
+        <v>7839</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>378.980853595485</v>
+        <v>384.0178886326881</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>867</v>
+        <v>45.75</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45.07429410514409</v>
+        <v>48.82833316893743</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>25.96071554736905</v>
+        <v>11.3020451412452</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.8940172266708055</v>
+        <v>1.686103248940633</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>9.566595891730088</v>
+        <v>0.3973073263924779</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7722</v>
+        <v>7822</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>375.1326618442034</v>
+        <v>378.980853595485</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>274.5</v>
+        <v>867</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>40.44621205327092</v>
+        <v>45.07429410514409</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>24.44646011977668</v>
+        <v>25.96071554736905</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4441587542674199</v>
+        <v>0.8940172266708055</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-2.2729547052638</v>
+        <v>9.566595891730088</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7795</v>
+        <v>7722</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>365.2484154512503</v>
+        <v>375.1326618442034</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>421</v>
+        <v>274.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>47.3968311202843</v>
+        <v>40.44621205327092</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>23.88480717112544</v>
+        <v>24.44646011977668</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9962952319046684</v>
+        <v>0.4441587542674199</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-2.200723070030008</v>
+        <v>-2.2729547052638</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6869</v>
+        <v>7795</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>364.2068916323527</v>
+        <v>365.2484154512503</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>67.8</v>
+        <v>421</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.47458016924729</v>
+        <v>47.3968311202843</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.45075457267674</v>
+        <v>23.88480717112544</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.6629391551698346</v>
+        <v>0.9962952319046684</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.4788980653800743</v>
+        <v>-2.200723070030008</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>8040</v>
+        <v>6869</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>360.7176196909776</v>
+        <v>364.2068916323527</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>72.2</v>
+        <v>67.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>41.66332251955737</v>
+        <v>44.47458016924729</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.30164781043748</v>
+        <v>21.45075457267674</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4149686616580608</v>
+        <v>0.6629391551698346</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.6472108955066398</v>
+        <v>0.4788980653800743</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6994</v>
+        <v>8040</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>355.9712893797886</v>
+        <v>360.7176196909776</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>35.95</v>
+        <v>72.2</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>26.68389101411101</v>
+        <v>41.66332251955737</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>37.00129240159534</v>
+        <v>28.30164781043748</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.684432203429566</v>
+        <v>0.4149686616580608</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.1603108347648518</v>
+        <v>0.6472108955066398</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6894</v>
+        <v>6994</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>350.7789125834673</v>
+        <v>355.9712893797886</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>352.5</v>
+        <v>35.95</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.77183434031223</v>
+        <v>26.68389101411101</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>17.22532049111586</v>
+        <v>37.00129240159534</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.4968230717743265</v>
+        <v>1.684432203429566</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>4.398916497212351</v>
+        <v>0.1603108347648518</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6962</v>
+        <v>6894</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>349.5251440370055</v>
+        <v>350.7789125834673</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>31.35</v>
+        <v>352.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>40.08668846863281</v>
+        <v>55.77183434031223</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>28.57498929436797</v>
+        <v>17.22532049111586</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.4801092977735114</v>
+        <v>0.4968230717743265</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0275112487163107</v>
+        <v>4.398916497212351</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6903</v>
+        <v>6962</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>348.960969627078</v>
+        <v>349.5251440370055</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>326</v>
+        <v>31.35</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>44.31497842911599</v>
+        <v>40.08668846863281</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>22.96191945826113</v>
+        <v>28.57498929436797</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.4211534955712626</v>
+        <v>0.4801092977735114</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-1.105546031636507</v>
+        <v>0.0275112487163107</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6901</v>
+        <v>6903</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>348.1060177888945</v>
+        <v>348.960969627078</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>17.5</v>
+        <v>326</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>51.16606809255144</v>
+        <v>44.31497842911599</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>22.01328033047774</v>
+        <v>22.96191945826113</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3236179507382224</v>
+        <v>0.4211534955712626</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-0.0931643248794617</v>
+        <v>-1.105546031636507</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>7769</v>
+        <v>6901</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>339.3308335349166</v>
+        <v>348.1060177888945</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>6475</v>
+        <v>17.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>51.92923727506181</v>
+        <v>51.16606809255144</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>13.53447313885111</v>
+        <v>22.01328033047774</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.6273312532929181</v>
+        <v>0.3236179507382224</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>67.94686559627286</v>
+        <v>-0.0931643248794617</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7547</v>
+        <v>7769</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>320.6603372879266</v>
+        <v>339.3308335349166</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>49.4</v>
+        <v>6475</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>40.35671512282345</v>
+        <v>51.92923727506181</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>26.92424438030663</v>
+        <v>13.53447313885111</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6245874466430992</v>
+        <v>0.6273312532929181</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>0.0050983765358965</v>
+        <v>67.94686559627286</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7768</v>
+        <v>7547</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>318.7404774123324</v>
+        <v>320.6603372879266</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>263.5</v>
+        <v>49.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>35.10828995517748</v>
+        <v>40.35671512282345</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45.20792222525858</v>
+        <v>26.92424438030663</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.4810012235385923</v>
+        <v>0.6245874466430992</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,7 +2849,7 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.1697773640165607</v>
+        <v>0.0050983765358965</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2859,21 +2859,21 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>7734</v>
+        <v>7768</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>317.2923186948292</v>
+        <v>318.7404774123324</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>3390</v>
+        <v>263.5</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.96519230413523</v>
+        <v>35.10828995517748</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>11.70730682057665</v>
+        <v>45.20792222525858</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5135748099546308</v>
+        <v>0.4810012235385923</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>44.82502034332393</v>
+        <v>0.1697773640165607</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6877</v>
+        <v>7734</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>315.8359442968631</v>
+        <v>317.2923186948292</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>125</v>
+        <v>3390</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>50.00337107797606</v>
+        <v>53.96519230413523</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>19.96993603859618</v>
+        <v>11.70730682057665</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.5300413248728005</v>
+        <v>0.5135748099546308</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.9836624918198726</v>
+        <v>44.82502034332393</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>7738</v>
+        <v>6877</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>314.5724760911185</v>
+        <v>315.8359442968631</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>166</v>
+        <v>125</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>46.09898641743239</v>
+        <v>50.00337107797606</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>28.36667305391017</v>
+        <v>19.96993603859618</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6532517824182983</v>
+        <v>0.5300413248728005</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0517735953395385</v>
+        <v>0.9836624918198726</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7732</v>
+        <v>7738</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>311.530229110045</v>
+        <v>314.5724760911185</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>35.6</v>
+        <v>166</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.66765405469216</v>
+        <v>46.09898641743239</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4.248958846804794</v>
+        <v>28.36667305391017</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.3744799409819613</v>
+        <v>0.6532517824182983</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.1033083818709986</v>
+        <v>0.0517735953395385</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7780</v>
+        <v>7732</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>308.0065588751249</v>
+        <v>311.530229110045</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>16.7</v>
+        <v>35.6</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>34.41287261156339</v>
+        <v>51.66765405469216</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>34.68928884007205</v>
+        <v>4.248958846804794</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.7038863364735299</v>
+        <v>0.3744799409819613</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-0.0266161523257199</v>
+        <v>-0.1033083818709986</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7730</v>
+        <v>7780</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>306.0647014455389</v>
+        <v>308.0065588751249</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>160</v>
+        <v>16.7</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>45.145780345227</v>
+        <v>34.41287261156339</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>26.34183615751398</v>
+        <v>34.68928884007205</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.6732730512439355</v>
+        <v>0.7038863364735299</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.3783002079062534</v>
+        <v>-0.0266161523257199</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7703</v>
+        <v>7730</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>300.1024305058731</v>
+        <v>306.0647014455389</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>181.5</v>
+        <v>160</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.75616891099163</v>
+        <v>45.145780345227</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>23.27557185143608</v>
+        <v>26.34183615751398</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7060234084338984</v>
+        <v>0.6732730512439355</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3624092339700571</v>
+        <v>0.3783002079062534</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6965</v>
+        <v>7703</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>297.9205350100312</v>
+        <v>300.1024305058731</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>76.7</v>
+        <v>181.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>43.10320449912296</v>
+        <v>49.75616891099163</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>32.0436375947092</v>
+        <v>23.27557185143608</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.8299642077602267</v>
+        <v>0.7060234084338984</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-0.1930710063605148</v>
+        <v>0.3624092339700571</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6861</v>
+        <v>6965</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>289.7836289565219</v>
+        <v>297.9205350100312</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>210.5</v>
+        <v>76.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>39.48057074665656</v>
+        <v>43.10320449912296</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>31.25976786526587</v>
+        <v>32.0436375947092</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.4966535815561014</v>
+        <v>0.8299642077602267</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>4.488629855965797</v>
+        <v>-0.1930710063605148</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>8042</v>
+        <v>6861</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>289.5138465285839</v>
+        <v>289.7836289565219</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>112.5</v>
+        <v>210.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>41.87284412490635</v>
+        <v>39.48057074665656</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.96987754738852</v>
+        <v>31.25976786526587</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6546888449904362</v>
+        <v>0.4966535815561014</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.0876335449390257</v>
+        <v>4.488629855965797</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7820</v>
+        <v>8042</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>288.7437472221413</v>
+        <v>289.5138465285839</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>34.42886462297426</v>
+        <v>41.87284412490635</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>20.96911671546224</v>
+        <v>27.96987754738852</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.203452329712263</v>
+        <v>0.6546888449904362</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.1944548393208709</v>
+        <v>-0.0876335449390257</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6895</v>
+        <v>7820</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>287.0162642051488</v>
+        <v>288.7437472221413</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>33.75872070493166</v>
+        <v>34.42886462297426</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>28.60643950116292</v>
+        <v>20.96911671546224</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.6812371433631372</v>
+        <v>0.203452329712263</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.7432472037848719</v>
+        <v>-0.1944548393208709</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>8028</v>
+        <v>6895</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>286.0919856092881</v>
+        <v>287.0162642051488</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>274.5</v>
+        <v>117</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>46.29288361706053</v>
+        <v>33.75872070493166</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.63992016740638</v>
+        <v>28.60643950116292</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.086486774441947</v>
+        <v>0.6812371433631372</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-2.048966906937729</v>
+        <v>0.7432472037848719</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7556</v>
+        <v>8028</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>277.7262114568037</v>
+        <v>286.0919856092881</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>223</v>
+        <v>274.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>44.06656294325315</v>
+        <v>46.29288361706053</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>34.97770777615629</v>
+        <v>17.63992016740638</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.2558229589043534</v>
+        <v>1.086486774441947</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>2.267337432412418</v>
+        <v>-2.048966906937729</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7788</v>
+        <v>7556</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>273.4679241713083</v>
+        <v>277.7262114568037</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>48.9837425496517</v>
+        <v>44.06656294325315</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.35594590849081</v>
+        <v>34.97770777615629</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.5602148208411265</v>
+        <v>0.2558229589043534</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.5711889429838628</v>
+        <v>2.267337432412418</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6944</v>
+        <v>7788</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>273.0872020041465</v>
+        <v>273.4679241713083</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>794</v>
+        <v>218</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>42.97045221626662</v>
+        <v>48.9837425496517</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.62153646055731</v>
+        <v>24.35594590849081</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4372332334288257</v>
+        <v>0.5602148208411265</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-5.269240586465443</v>
+        <v>-0.5711889429838628</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6936</v>
+        <v>6944</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>271.6450485574047</v>
+        <v>273.0872020041465</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>31.9</v>
+        <v>794</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>44.53982686721466</v>
+        <v>42.97045221626662</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.96379189019574</v>
+        <v>24.62153646055731</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.045315299080974</v>
+        <v>0.4372332334288257</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0483370542407218</v>
+        <v>-5.269240586465443</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>7631</v>
+        <v>6936</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>271.4589128659065</v>
+        <v>271.6450485574047</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>132</v>
+        <v>31.9</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>43.19870122646992</v>
+        <v>44.53982686721466</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>11.34447549867436</v>
+        <v>13.96379189019574</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.3808430345660598</v>
+        <v>1.045315299080974</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-1.025822184190734</v>
+        <v>0.0483370542407218</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6859</v>
+        <v>7631</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>271.3559526894729</v>
+        <v>271.4589128659065</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101</v>
+        <v>132</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>37.91337930796868</v>
+        <v>43.19870122646992</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28.48061431104629</v>
+        <v>11.34447549867436</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.1099644115177269</v>
+        <v>0.3808430345660598</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.8050633386185355</v>
+        <v>-1.025822184190734</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6924</v>
+        <v>6859</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>271.1114577936602</v>
+        <v>271.3559526894729</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>52.30188074947451</v>
+        <v>37.91337930796868</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>20.98842289632559</v>
+        <v>28.48061431104629</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.144297427313323</v>
+        <v>0.1099644115177269</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>1.534915739877025</v>
+        <v>0.8050633386185355</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6902</v>
+        <v>6924</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>271.0786166865307</v>
+        <v>271.1114577936602</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>123.5</v>
+        <v>114</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>48.71648201742233</v>
+        <v>52.30188074947451</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>18.38353078346206</v>
+        <v>20.98842289632559</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.053638944374307</v>
+        <v>1.144297427313323</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.463035229156068</v>
+        <v>1.534915739877025</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7842</v>
+        <v>6902</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>265.6653965554325</v>
+        <v>271.0786166865307</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>75.8</v>
+        <v>123.5</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>43.38593683876494</v>
+        <v>48.71648201742233</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>11.10232481050481</v>
+        <v>18.38353078346206</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.027073883954842</v>
+        <v>1.053638944374307</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.2517427119138107</v>
+        <v>0.463035229156068</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6937</v>
+        <v>7842</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>262.5425636849615</v>
+        <v>265.6653965554325</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>262.5</v>
+        <v>75.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.57271700917669</v>
+        <v>43.38593683876494</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>9.731788469700682</v>
+        <v>11.10232481050481</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.5308716521365752</v>
+        <v>1.027073883954842</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.213227412629303</v>
+        <v>-0.2517427119138107</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7747</v>
+        <v>6937</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>261.8988232621346</v>
+        <v>262.5425636849615</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>116</v>
+        <v>262.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>51.41939836117258</v>
+        <v>48.57271700917669</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.03464540150884</v>
+        <v>9.731788469700682</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.2522395393667553</v>
+        <v>0.5308716521365752</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.1273922273441012</v>
+        <v>-0.213227412629303</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6921</v>
+        <v>7747</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>258.3963865196977</v>
+        <v>261.8988232621346</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>64.5</v>
+        <v>116</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>49.78432109287554</v>
+        <v>51.41939836117258</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>29.29914381340418</v>
+        <v>18.03464540150884</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>1.631828208509614</v>
+        <v>0.2522395393667553</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.390409359102891</v>
+        <v>-0.1273922273441012</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6909</v>
+        <v>6921</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>251.8321340626823</v>
+        <v>258.3963865196977</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>40.85</v>
+        <v>64.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.46852024334984</v>
+        <v>49.78432109287554</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>31.18780219321077</v>
+        <v>29.29914381340418</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4106463103333529</v>
+        <v>1.631828208509614</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.09810257177819801</v>
+        <v>0.390409359102891</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>volume_break, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6919</v>
+        <v>6909</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>250.5567833992044</v>
+        <v>251.8321340626823</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>107.5</v>
+        <v>40.85</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>54.66951580107126</v>
+        <v>38.46852024334984</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>16.05622585620942</v>
+        <v>31.18780219321077</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.5649563309131493</v>
+        <v>0.4106463103333529</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>0.3747471833904281</v>
+        <v>0.09810257177819801</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6933</v>
+        <v>6919</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>248.8694780203097</v>
+        <v>250.5567833992044</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>169</v>
+        <v>107.5</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.71920224589245</v>
+        <v>54.66951580107126</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.33695837936965</v>
+        <v>16.05622585620942</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5292307197141903</v>
+        <v>0.5649563309131493</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.8911905192230181</v>
+        <v>0.3747471833904281</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6899</v>
+        <v>6933</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>246.2387510434666</v>
+        <v>248.8694780203097</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>50.9</v>
+        <v>169</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.01452615140264</v>
+        <v>55.71920224589245</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.29037111191558</v>
+        <v>12.33695837936965</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.1754882454766813</v>
+        <v>0.5292307197141903</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.2796905324567529</v>
+        <v>0.8911905192230181</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6951</v>
+        <v>6899</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>244.1807003623512</v>
+        <v>246.2387510434666</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>70.8</v>
+        <v>50.9</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>32.61866467648575</v>
+        <v>39.01452615140264</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.01890431642084</v>
+        <v>25.29037111191558</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.817356115453183</v>
+        <v>0.1754882454766813</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.1416846773569064</v>
+        <v>0.2796905324567529</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4449,21 +4449,21 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6865</v>
+        <v>6951</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>243.7049995619366</v>
+        <v>244.1807003623512</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>24.75</v>
+        <v>70.8</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>51.06148916062954</v>
+        <v>32.61866467648575</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.776176847506129</v>
+        <v>39.01890431642084</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.0646156477560315</v>
+        <v>0.817356115453183</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.7177605482044402</v>
+        <v>0.1416846773569064</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>7827</v>
+        <v>6865</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>239.0555023699349</v>
+        <v>243.7049995619366</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>156.5</v>
+        <v>24.75</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>52.42481054785771</v>
+        <v>51.06148916062954</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>16.41142288422823</v>
+        <v>8.776176847506129</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.085360816859852</v>
+        <v>0.0646156477560315</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.7805579633272415</v>
+        <v>0.7177605482044402</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7721</v>
+        <v>7827</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>237.3518143410534</v>
+        <v>239.0555023699349</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>61.4</v>
+        <v>156.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>42.80190513028729</v>
+        <v>52.42481054785771</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>26.43506184819369</v>
+        <v>16.41142288422823</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.4118388078209144</v>
+        <v>1.085360816859852</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>0.3564675813253237</v>
+        <v>0.7805579633272415</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7749</v>
+        <v>7721</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>236.8430241771023</v>
+        <v>237.3518143410534</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>347.5</v>
+        <v>61.4</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>40.62237260798368</v>
+        <v>42.80190513028729</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>34.46681585429653</v>
+        <v>26.43506184819369</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.3406417745204819</v>
+        <v>0.4118388078209144</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>3.409192101332334</v>
+        <v>0.3564675813253237</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7818</v>
+        <v>7749</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>234.4502917609148</v>
+        <v>236.8430241771023</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>62</v>
+        <v>347.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>26.74928528181837</v>
+        <v>40.62237260798368</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>33.95477222183369</v>
+        <v>34.46681585429653</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5534880286379524</v>
+        <v>0.3406417745204819</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.6405295583996046</v>
+        <v>3.409192101332334</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6931</v>
+        <v>7818</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>233.8561402064316</v>
+        <v>234.4502917609148</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>37.3</v>
+        <v>62</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>36.74116661561253</v>
+        <v>26.74928528181837</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>20.90613057907495</v>
+        <v>33.95477222183369</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.105887083605101</v>
+        <v>0.5534880286379524</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,7 +4757,7 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.0638265245805663</v>
+        <v>-0.6405295583996046</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -4767,21 +4767,21 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7803</v>
+        <v>6931</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>230.8609300269833</v>
+        <v>233.8561402064316</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>20.7</v>
+        <v>37.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45.22657770840713</v>
+        <v>36.74116661561253</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>22.27462824618389</v>
+        <v>20.90613057907495</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.6082988354369759</v>
+        <v>1.105887083605101</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.02841724585499</v>
+        <v>-0.0638265245805663</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6885</v>
+        <v>7803</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>228.8954504155463</v>
+        <v>230.8609300269833</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.24804961194404</v>
+        <v>45.22657770840713</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>11.0633659487103</v>
+        <v>22.27462824618389</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5991466593160778</v>
+        <v>0.6082988354369759</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.0581685829823419</v>
+        <v>0.02841724585499</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7821</v>
+        <v>6885</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>227.1077775620772</v>
+        <v>228.8954504155463</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>40.15</v>
+        <v>21</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>41.5928963002428</v>
+        <v>47.24804961194404</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>19.50379681900669</v>
+        <v>11.0633659487103</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.333835816553983</v>
+        <v>0.5991466593160778</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.1003250803720926</v>
+        <v>0.0581685829823419</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6908</v>
+        <v>7821</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>226.933901996451</v>
+        <v>227.1077775620772</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>33.6</v>
+        <v>40.15</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>36.96443874000483</v>
+        <v>41.5928963002428</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>29.85695589638636</v>
+        <v>19.50379681900669</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2583616093068347</v>
+        <v>1.333835816553983</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.09245621826629109</v>
+        <v>0.1003250803720926</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6870</v>
+        <v>6908</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>225.1125380937005</v>
+        <v>226.933901996451</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>261.5</v>
+        <v>33.6</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>48.71332909618442</v>
+        <v>36.96443874000483</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>18.17316137500057</v>
+        <v>29.85695589638636</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.234715434631002</v>
+        <v>0.2583616093068347</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.86159880209577</v>
+        <v>-0.09245621826629109</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6890</v>
+        <v>6870</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>223.967489973851</v>
+        <v>225.1125380937005</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>170.5</v>
+        <v>261.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.89509692563947</v>
+        <v>48.71332909618442</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15.57373042789482</v>
+        <v>18.17316137500057</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.4245897430055731</v>
+        <v>1.234715434631002</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.7811728363126846</v>
+        <v>-1.86159880209577</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6923</v>
+        <v>6890</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>223.6501922809645</v>
+        <v>223.967489973851</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>170.5</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.97872655754299</v>
+        <v>41.89509692563947</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>12.4300018527405</v>
+        <v>15.57373042789482</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5047003484879381</v>
+        <v>0.4245897430055731</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.3384561481432115</v>
+        <v>0.7811728363126846</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7740</v>
+        <v>6923</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>223.2402188142815</v>
+        <v>223.6501922809645</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>155</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>52.67603514597398</v>
+        <v>43.97872655754299</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.82462673012334</v>
+        <v>12.4300018527405</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6829241170152272</v>
+        <v>0.5047003484879381</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.9849376946577872</v>
+        <v>-0.3384561481432115</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6906</v>
+        <v>7740</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>219.4513576685233</v>
+        <v>223.2402188142815</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>73.7</v>
+        <v>155</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.44216573840384</v>
+        <v>52.67603514597398</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>31.32707248581766</v>
+        <v>14.82462673012334</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.496536451296112</v>
+        <v>0.6829241170152272</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.7136412210628329</v>
+        <v>0.9849376946577872</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7810</v>
+        <v>6906</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>217.0248658078642</v>
+        <v>219.4513576685233</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>196</v>
+        <v>73.7</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>51.49004482863162</v>
+        <v>46.44216573840384</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.78183950859578</v>
+        <v>31.32707248581766</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.839177837910894</v>
+        <v>0.496536451296112</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.874570391240387</v>
+        <v>0.7136412210628329</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>8024</v>
+        <v>7810</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>214.5741679829212</v>
+        <v>217.0248658078642</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14.55</v>
+        <v>196</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>47.65393815293463</v>
+        <v>51.49004482863162</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>20.46157342412248</v>
+        <v>14.78183950859578</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.1405386687384039</v>
+        <v>0.839177837910894</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>1</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1770923111336658</v>
+        <v>0.874570391240387</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>macd_golden_cross, market_above_ma60, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6916</v>
+        <v>8024</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>209.1679969370884</v>
+        <v>214.5741679829212</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>18.2</v>
+        <v>14.55</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>42.52424161536517</v>
+        <v>47.65393815293463</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.47409331036239</v>
+        <v>20.46157342412248</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.3138018478653101</v>
+        <v>0.1405386687384039</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.0949561647126375</v>
+        <v>-0.1770923111336658</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6887</v>
+        <v>6916</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>208.239612121349</v>
+        <v>209.1679969370884</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>36.45</v>
+        <v>18.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.23604540051819</v>
+        <v>42.52424161536517</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>16.64856655344304</v>
+        <v>15.47409331036239</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.1689950929161704</v>
+        <v>0.3138018478653101</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.1468550452275275</v>
+        <v>-0.0949561647126375</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7744</v>
+        <v>6887</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>204.9249317936656</v>
+        <v>208.239612121349</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>450.5</v>
+        <v>36.45</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>56.78162942539351</v>
+        <v>49.23604540051819</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.98608842087897</v>
+        <v>16.64856655344304</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>1.274410672952227</v>
+        <v>0.1689950929161704</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>5.420502976165299</v>
+        <v>-0.1468550452275275</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7791</v>
+        <v>7744</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>204.8688934209966</v>
+        <v>204.9249317936656</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>59.6</v>
+        <v>450.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>31.91687058981212</v>
+        <v>56.78162942539351</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>24.40248762173679</v>
+        <v>19.98608842087897</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.8176014851955725</v>
+        <v>1.274410672952227</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-0.2023818892200859</v>
+        <v>5.420502976165299</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>8011</v>
+        <v>7791</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>197.7617026107613</v>
+        <v>204.8688934209966</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>16.4</v>
+        <v>59.6</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>45.03458307024442</v>
+        <v>31.91687058981212</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>28.8152866937754</v>
+        <v>24.40248762173679</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.327607368034113</v>
+        <v>0.8176014851955725</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.08867668885707131</v>
+        <v>-0.2023818892200859</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7786</v>
+        <v>8011</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>197.2187608605284</v>
+        <v>197.7617026107613</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>123.5</v>
+        <v>16.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.19232325979996</v>
+        <v>45.03458307024442</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>13.56487892317752</v>
+        <v>28.8152866937754</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.5603921467805</v>
+        <v>0.327607368034113</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.6396189816423516</v>
+        <v>0.08867668885707131</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6967</v>
+        <v>7786</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>187.6636792474111</v>
+        <v>197.2187608605284</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>69</v>
+        <v>123.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>44.00706318997158</v>
+        <v>45.19232325979996</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.32561487614958</v>
+        <v>13.56487892317752</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.4904097045248955</v>
+        <v>1.5603921467805</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.4672753295599031</v>
+        <v>-0.6396189816423516</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>7805</v>
+        <v>6967</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>184.4607853796337</v>
+        <v>187.6636792474111</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>642</v>
+        <v>69</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>54.72970673185532</v>
+        <v>44.00706318997158</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>31.29094696048634</v>
+        <v>16.32561487614958</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.7314629381702484</v>
+        <v>0.4904097045248955</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>7.273845970654168</v>
+        <v>-0.4672753295599031</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6997</v>
+        <v>7805</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>176.3116728472289</v>
+        <v>184.4607853796337</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>70.90000000000001</v>
+        <v>642</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>52.72153441895443</v>
+        <v>54.72970673185532</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>11.81614683905378</v>
+        <v>31.29094696048634</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>4.355763060650985</v>
+        <v>0.7314629381702484</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>3.923615279257851</v>
+        <v>7.273845970654168</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6862</v>
+        <v>6997</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>172.9691232384678</v>
+        <v>176.3116728472289</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>144</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>43.9415030603054</v>
+        <v>52.72153441895443</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>24.63591405555075</v>
+        <v>11.81614683905378</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.3998352533486989</v>
+        <v>4.355763060650985</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>1.534706510471013</v>
+        <v>3.923615279257851</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>volume_break, market_above_ma60, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7799</v>
+        <v>6862</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>170.8819322053963</v>
+        <v>172.9691232384678</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>357</v>
+        <v>144</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>42.3139589566189</v>
+        <v>43.9415030603054</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.01531886023358</v>
+        <v>24.63591405555075</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.3332931175341063</v>
+        <v>0.3998352533486989</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,7 +5923,7 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-5.624303623924119</v>
+        <v>1.534706510471013</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
@@ -5933,21 +5933,21 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>8032</v>
+        <v>7799</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>166.0809554078076</v>
+        <v>170.8819322053963</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>36.3</v>
+        <v>357</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>42.12999495272889</v>
+        <v>42.3139589566189</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>33.66124101023824</v>
+        <v>22.01531886023358</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.382165097099353</v>
+        <v>0.3332931175341063</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.2458067837360724</v>
+        <v>-5.624303623924119</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7760</v>
+        <v>8032</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>151.0597103683878</v>
+        <v>166.0809554078076</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>33.65</v>
+        <v>36.3</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>45.5854740795683</v>
+        <v>42.12999495272889</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>16.20842471866507</v>
+        <v>33.66124101023824</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.25444515219362</v>
+        <v>0.382165097099353</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1559135733476741</v>
+        <v>0.2458067837360724</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6934</v>
+        <v>7760</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>150.0764426246642</v>
+        <v>151.0597103683878</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>73.2</v>
+        <v>33.65</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>45.53213616389399</v>
+        <v>45.5854740795683</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>16.41410394127492</v>
+        <v>16.20842471866507</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.7206101866548456</v>
+        <v>1.25444515219362</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.7202095714211663</v>
+        <v>-0.1559135733476741</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>7772</v>
+        <v>6934</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>146.8992368316038</v>
+        <v>150.0764426246642</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>94.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>39.08318708354716</v>
+        <v>45.53213616389399</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>29.95941951271729</v>
+        <v>16.41410394127492</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.3988944001494741</v>
+        <v>0.7206101866548456</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>1.697310158822001</v>
+        <v>-0.7202095714211663</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7402</v>
+        <v>7772</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>145.4173480516554</v>
+        <v>146.8992368316038</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>104.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.3950448823861</v>
+        <v>39.08318708354716</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>21.50000052803292</v>
+        <v>29.95941951271729</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.1378387616877435</v>
+        <v>0.3988944001494741</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>-1.365179129423035</v>
+        <v>1.697310158822001</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6953</v>
+        <v>7402</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>145.3622759195572</v>
+        <v>145.4173480516554</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>215.5</v>
+        <v>104.5</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>47.58706670455423</v>
+        <v>45.3950448823861</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>11.00226174886737</v>
+        <v>21.50000052803292</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.4651371079697273</v>
+        <v>0.1378387616877435</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.6734575891230605</v>
+        <v>-1.365179129423035</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7736</v>
+        <v>6953</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>138.446179188635</v>
+        <v>145.3622759195572</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>215.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>42.96981784371774</v>
+        <v>47.58706670455423</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>20.59661208077651</v>
+        <v>11.00226174886737</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.4665610529908192</v>
+        <v>0.4651371079697273</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.0258222666864123</v>
+        <v>0.6734575891230605</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6983</v>
+        <v>7736</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>136.0340597696882</v>
+        <v>138.446179188635</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>304</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>39.5075834097345</v>
+        <v>42.96981784371774</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.59596061314196</v>
+        <v>20.59661208077651</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.6756605559292406</v>
+        <v>0.4665610529908192</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.2784049780002409</v>
+        <v>0.0258222666864123</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7765</v>
+        <v>6983</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>133.666212618466</v>
+        <v>136.0340597696882</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>222</v>
+        <v>304</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>43.13195313212148</v>
+        <v>39.5075834097345</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.38254561238986</v>
+        <v>12.59596061314196</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6952033851251688</v>
+        <v>0.6756605559292406</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1535372326994593</v>
+        <v>-0.2784049780002409</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>7753</v>
+        <v>7765</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>131.5260479413047</v>
+        <v>133.666212618466</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>38.05</v>
+        <v>222</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>41.89900644860072</v>
+        <v>43.13195313212148</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>14.77239376575127</v>
+        <v>11.38254561238986</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5811037505736205</v>
+        <v>0.6952033851251688</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.1635294602425281</v>
+        <v>0.1535372326994593</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6873</v>
+        <v>7753</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>127.7479027949518</v>
+        <v>131.5260479413047</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>78.59999999999999</v>
+        <v>38.05</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.25663992889335</v>
+        <v>41.89900644860072</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>17.18081014209088</v>
+        <v>14.77239376575127</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.5489370055245011</v>
+        <v>0.5811037505736205</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.6021785140273126</v>
+        <v>-0.1635294602425281</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>7728</v>
+        <v>6873</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>124.5715306607673</v>
+        <v>127.7479027949518</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>624</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>49.8606867931443</v>
+        <v>41.25663992889335</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>19.10312878122456</v>
+        <v>17.18081014209088</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.2945679780387704</v>
+        <v>0.5489370055245011</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>4.478763575264193</v>
+        <v>-0.6021785140273126</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>8034</v>
+        <v>7728</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>120.409739784382</v>
+        <v>124.5715306607673</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19.55</v>
+        <v>624</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.54096201154466</v>
+        <v>49.8606867931443</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>36.72766957901302</v>
+        <v>19.10312878122456</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2134236710523545</v>
+        <v>0.2945679780387704</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.143111948293094</v>
+        <v>4.478763575264193</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>6918</v>
+        <v>8034</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>118.9023237125122</v>
+        <v>120.409739784382</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>19.55</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>45.40902769653241</v>
+        <v>43.54096201154466</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>13.97168990859129</v>
+        <v>36.72766957901302</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.5275258534829675</v>
+        <v>0.2134236710523545</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0385634270947037</v>
+        <v>0.143111948293094</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6854</v>
+        <v>6918</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>112.2142162337256</v>
+        <v>118.9023237125122</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>97</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>40.35159199915236</v>
+        <v>45.40902769653241</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>41.93338956490491</v>
+        <v>13.97168990859129</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.4024576072894771</v>
+        <v>0.5275258534829675</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.221249830184383</v>
+        <v>-0.0385634270947037</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6988</v>
+        <v>6854</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>107.8289891549108</v>
+        <v>112.2142162337256</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>12.65</v>
+        <v>97</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>50.79930887566243</v>
+        <v>40.35159199915236</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>11.42872327040735</v>
+        <v>41.93338956490491</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.311064896073524</v>
+        <v>0.4024576072894771</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.1919658895087103</v>
+        <v>1.221249830184383</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6971</v>
+        <v>6988</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>104.0882462793198</v>
+        <v>107.8289891549108</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>25.5</v>
+        <v>12.65</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>31.6008897027615</v>
+        <v>50.79930887566243</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.5351502769122</v>
+        <v>11.42872327040735</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.9601709537457496</v>
+        <v>1.311064896073524</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1218595228932696</v>
+        <v>0.1919658895087103</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>8038</v>
+        <v>6971</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>81.15555910427356</v>
+        <v>104.0882462793198</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>32.25</v>
+        <v>25.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>35.14682782398403</v>
+        <v>31.6008897027615</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.85626801009762</v>
+        <v>16.5351502769122</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.42049819703179</v>
+        <v>0.9601709537457496</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>1</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.3138665503626403</v>
+        <v>-0.1218595228932696</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6928</v>
+        <v>8038</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>81.05087844246114</v>
+        <v>81.15555910427356</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>48.4</v>
+        <v>32.25</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>45.78172889675934</v>
+        <v>35.14682782398403</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>18.88930377020059</v>
+        <v>20.85626801009762</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.181447058689112</v>
+        <v>0.42049819703179</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.4739124823458961</v>
+        <v>-0.3138665503626403</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, mfi_strong</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7770</v>
+        <v>6928</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>74.36195111235853</v>
+        <v>81.05087844246114</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>39.4</v>
+        <v>48.4</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>52.1593048736386</v>
+        <v>45.78172889675934</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>13.90501183429123</v>
+        <v>18.88930377020059</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5561763828059387</v>
+        <v>0.181447058689112</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-1.604685303361799</v>
+        <v>-0.4739124823458961</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
+          <t>market_above_ma60, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>6925</v>
+        <v>7770</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>71.78692020731883</v>
+        <v>74.36195111235853</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>53.9</v>
+        <v>39.4</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,16 +7018,16 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>44.38721027036748</v>
+        <v>52.1593048736386</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>17.85206614943042</v>
+        <v>13.90501183429123</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.7532189401655829</v>
+        <v>0.5561763828059387</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
         <v>0</v>
@@ -7036,62 +7036,115 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.235374555915516</v>
+        <v>-1.604685303361799</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>6925</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>意藍</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>71.78692020731883</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>44.38721027036748</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>17.85206614943042</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.7532189401655829</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.235374555915516</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>7823</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>奧義賽博-KY創</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>58.69150387738266</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
         <v>55.90183596543188</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>18.9229164701944</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>0.4946995249037921</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
         <v>0.4549050763267028</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>rsi_strong, market_above_ma60</t>
         </is>
